--- a/dataset_t6_grouped/results2/G5/G5_T8387_W0075F0003T0006Z000C1N63_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T8387_W0075F0003T0006Z000C1N63_analysis.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H3"/>
+  <dimension ref="A1:H5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>29.0925314858857</v>
+        <v>5.188143415161918</v>
       </c>
       <c r="D2" t="n">
-        <v>29.25623725405733</v>
+        <v>8.875919046255433</v>
       </c>
       <c r="E2" t="n">
-        <v>0.7689915581445295</v>
+        <v>10.76414771454988</v>
       </c>
       <c r="F2" t="n">
-        <v>0.7262088019274326</v>
+        <v>9.691374056685067</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,23 +512,87 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
+        <v>29.0925314858857</v>
+      </c>
+      <c r="D3" t="n">
+        <v>29.25623725405733</v>
+      </c>
+      <c r="E3" t="n">
+        <v>10.76414771454988</v>
+      </c>
+      <c r="F3" t="n">
+        <v>9.691374056685067</v>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>T8387</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>G5</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>W0075F0003T0006Z000C1N63.png</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>3</v>
+      </c>
+      <c r="C4" t="n">
         <v>30.63051460217476</v>
       </c>
-      <c r="D3" t="n">
+      <c r="D4" t="n">
         <v>30.7086548579122</v>
       </c>
-      <c r="E3" t="n">
-        <v>0.7689915581445295</v>
-      </c>
-      <c r="F3" t="n">
-        <v>0.7262088019274326</v>
-      </c>
-      <c r="G3" t="inlineStr">
+      <c r="E4" t="n">
+        <v>10.76414771454988</v>
+      </c>
+      <c r="F4" t="n">
+        <v>9.691374056685067</v>
+      </c>
+      <c r="G4" t="inlineStr">
         <is>
           <t>T8387</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr">
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>G5</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>W0075F0003T0006Z000C1N63.png</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>4</v>
+      </c>
+      <c r="C5" t="n">
+        <v>12.96262819982629</v>
+      </c>
+      <c r="D5" t="n">
+        <v>12.77207624320586</v>
+      </c>
+      <c r="E5" t="n">
+        <v>10.76414771454988</v>
+      </c>
+      <c r="F5" t="n">
+        <v>9.691374056685067</v>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>T8387</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
         <is>
           <t>G5</t>
         </is>

--- a/dataset_t6_grouped/results2/G5/G5_T8387_W0075F0003T0006Z000C1N63_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G5/G5_T8387_W0075F0003T0006Z000C1N63_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>5.188143415161918</v>
+        <v>0.8430733049638117</v>
       </c>
       <c r="D2" t="n">
-        <v>8.875919046255433</v>
+        <v>1.442336845016508</v>
       </c>
       <c r="E2" t="n">
-        <v>10.76414771454988</v>
+        <v>1.749174003614356</v>
       </c>
       <c r="F2" t="n">
-        <v>9.691374056685067</v>
+        <v>1.574848284211324</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>29.0925314858857</v>
+        <v>4.727536366456427</v>
       </c>
       <c r="D3" t="n">
-        <v>29.25623725405733</v>
+        <v>4.754138553784316</v>
       </c>
       <c r="E3" t="n">
-        <v>10.76414771454988</v>
+        <v>1.749174003614356</v>
       </c>
       <c r="F3" t="n">
-        <v>9.691374056685067</v>
+        <v>1.574848284211324</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>30.63051460217476</v>
+        <v>4.977458622853399</v>
       </c>
       <c r="D4" t="n">
-        <v>30.7086548579122</v>
+        <v>4.990156414410732</v>
       </c>
       <c r="E4" t="n">
-        <v>10.76414771454988</v>
+        <v>1.749174003614356</v>
       </c>
       <c r="F4" t="n">
-        <v>9.691374056685067</v>
+        <v>1.574848284211324</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>12.96262819982629</v>
+        <v>2.106427082471772</v>
       </c>
       <c r="D5" t="n">
-        <v>12.77207624320586</v>
+        <v>2.075462389520951</v>
       </c>
       <c r="E5" t="n">
-        <v>10.76414771454988</v>
+        <v>1.749174003614356</v>
       </c>
       <c r="F5" t="n">
-        <v>9.691374056685067</v>
+        <v>1.574848284211324</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
